--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,27 +568,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESEMPIO_CORE</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Esempio fondo/ETF core globale</t>
+          <t>Core Dividend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ETF/Fondo</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Core globale</t>
+          <t>Satellite income</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Core Globale</t>
+          <t>Dividend globale</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -620,11 +620,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>FTSE All-World / MSCI ACWI</t>
+          <t>VHYL / Global Dividend</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Riga di esempio. Sostituire con dati reali solo in app o in repo privato.</t>
+          <t>Ordine eseguito; ingresso/uscita 0; bollo una tantum 6 EUR</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -675,42 +675,42 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Per ESEMPIO_CORE: qual e' il ruolo nel portafoglio e con quale ETF/fondo lo confrontiamo?</t>
+          <t>Per LU0981915779: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESEMPIO_PAC</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Esempio PAC settoriale</t>
+          <t>Fineco AM Passive Underlyings 7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fondo/PAC</t>
+          <t>Fondo</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Satellite</t>
+          <t>Core gestito</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tecnologia e AI</t>
+          <t>Multi asset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>Una tantum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -737,11 +737,11 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>ETF/fondo settoriale coerente</t>
+          <t>MSCI World / Global multi asset</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Riga di esempio per PAC. Non pubblicare dati personali in repo pubblico.</t>
+          <t>Ordine eseguito; ingresso/uscita 0; bollo una tantum 6 EUR</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -787,15 +787,600 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Per IE0005TOUMC7: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IE000KTYLDC4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fineco AM Passive Underlyings 6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Core gestito</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Multi asset prudente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MSCI World / Global multi asset</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Ordine eseguito; ingresso/uscita 0; bollo una tantum 6 EUR</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Per IE000KTYLDC4: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Satellite Europa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Euro 50 / Europe equities</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Ordine eseguito; ingresso/uscita 0; bollo una tantum 6 EUR</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Per LU0261952682: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IE000DWG3DP6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fineco AM Passive Underlyings 8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Core gestito crescita</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Multi asset crescita</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MSCI World / Growth proxy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ordine eseguito; ingresso/uscita 0; bollo una tantum 6 EUR</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Punto zero: non valutare ancora il rendimento, verifica solo corretta esecuzione.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Per IE000DWG3DP6: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IE0003YRHWF4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sustainable Future Connectivity FAM Fund</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Satellite tematico</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tecnologia e AI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PAC</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>150</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Cloud / Nasdaq / AI proxy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>PAC 150 EUR/mese; ingresso/uscita 0; bollo una tantum 6 EUR</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>PAC impostato: attendere prima rata o confermare se gia' addebitata.</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Per ESEMPIO_PAC: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Per IE0003YRHWF4: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IE00BD2PJG29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAM MSCI Emerging Markets Index Fund</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fondo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Satellite geografico</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PAC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>150</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MSCI Emerging Markets proxy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>PAC 150 EUR/mese; ingresso/uscita 0; bollo una tantum 6 EUR</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>PAC impostato: attendere prima rata o confermare se gia' addebitata.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Per IE00BD2PJG29: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,7 +1473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AlphaForge v8 Fineco Portfolio Tracker</t>
+          <t>AlphaForge v9.1 Investing UI Portfolio Tracker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -902,19 +1487,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="F2" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G2" t="n">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="H2" t="n">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -923,17 +1508,17 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M2" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Portafoglio appena avviato: registra baseline, verifica costi/KID e non valutare ancora la performance. PAC programmato: 150 EUR/mese.</t>
+          <t>Portafoglio appena avviato: una tantum corretta e PAC attivi in baseline. Non valutare ancora la performance; controlla quote, NAV e costi. PAC programmato: 300 EUR/mese.</t>
         </is>
       </c>
     </row>
@@ -948,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,12 +1684,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESEMPIO_CORE</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Per ESEMPIO_CORE: qual e' il ruolo nel portafoglio e con quale ETF/fondo lo confrontiamo?</t>
+          <t>Per LU0981915779: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1119,15 +1704,115 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESEMPIO_PAC</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Per ESEMPIO_PAC: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+          <t>Per IE0005TOUMC7: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IE000KTYLDC4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Per IE000KTYLDC4: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Per LU0261952682: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IE000DWG3DP6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Per IE000DWG3DP6: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IE0003YRHWF4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Per IE0003YRHWF4: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IE00BD2PJG29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Per IE00BD2PJG29: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Domanda specifica sul singolo strumento.</t>
         </is>

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/AlphaForge_Fineco_Portfolio.xlsx
+++ b/AlphaForge_Fineco_Portfolio.xlsx
@@ -639,11 +639,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -756,11 +756,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -990,11 +990,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1107,11 +1107,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1341,11 +1341,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
